--- a/apps/quiz/static/quiz/quiz_import_template.xlsx
+++ b/apps/quiz/static/quiz/quiz_import_template.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -449,11 +449,12 @@
     <col width="28" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="42" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="42" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -499,25 +500,30 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>option_f</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>correct_option</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>explanation</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>difficulty</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>topic_tags</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>year_source</t>
         </is>
@@ -566,25 +572,30 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>MCQ/True-False: a b c d e | Fill blank: answer text | Matching/Essay: leave blank</t>
+          <t>MCQ: optional 6th choice. Fill when correct_option is f.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>MCQ: a b c d e f | True/False: a or b | Fill blank: answer text | Matching/Essay: leave blank</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
           <t>Shown to student after answering in practice mode</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>easy / medium / hard  (default: medium)</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Optional comma separated tags e.g. Definition, Basics</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>e.g. 2022</t>
         </is>
